--- a/AAII_Financials/Yearly/NYT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NYT_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>31500</v>
+        <v>22000</v>
       </c>
       <c r="E14" s="3">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="F14" s="3">
-        <v>22200</v>
+        <v>14600</v>
       </c>
       <c r="G14" s="3">
         <v>24200</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2357500</v>
+        <v>2366900</v>
       </c>
       <c r="E17" s="3">
-        <v>2197000</v>
+        <v>2204500</v>
       </c>
       <c r="F17" s="3">
-        <v>2097900</v>
+        <v>2105500</v>
       </c>
       <c r="G17" s="3">
         <v>2025500</v>
@@ -1179,13 +1179,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>440400</v>
+        <v>431000</v>
       </c>
       <c r="E18" s="3">
-        <v>361900</v>
+        <v>354400</v>
       </c>
       <c r="F18" s="3">
-        <v>301200</v>
+        <v>293600</v>
       </c>
       <c r="G18" s="3">
         <v>253800</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>525400</v>
+        <v>516000</v>
       </c>
       <c r="E21" s="3">
-        <v>444800</v>
+        <v>437300</v>
       </c>
       <c r="F21" s="3">
-        <v>389800</v>
+        <v>382200</v>
       </c>
       <c r="G21" s="3">
         <v>336400</v>
